--- a/local/templates/start/StartList.xlsx
+++ b/local/templates/start/StartList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/Misc/usaw-owlcms/local/templates/start/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Library/Application Support/owlcms/67.4.3+test/local/templates/start/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0435B5C-546A-FC48-B64A-70188C66A689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B96E670-7CD5-5D4E-BA42-82582B33AB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="500" windowWidth="39500" windowHeight="25100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,17 @@
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
           </rPr>
-          <t>jx:area(lastCell="K4")</t>
+          <t xml:space="preserve">jx:area(lastCell="K4")
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+          </rPr>
+          <t>owlcms:verticalBorders(4,1,11)</t>
         </r>
       </text>
     </comment>
